--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2438,6 +2438,116 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120107446</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillström, korpipele., Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>590246</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6927243</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -2443,7 +2443,7 @@
         <v>120107446</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2548,6 +2548,121 @@
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122670756</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57275</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100001</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Duvhök</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Astur gentilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Korpipele, vid mötesplats på vägen., Hällsjön, n:a Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>590339</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6927305</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fjädrar vid mötesplats efter Lillströmsvägen vid Korpipele. Hål i vallen vid sidan av vägen med blodspår längst in.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -1341,7 +1341,7 @@
         <v>119388484</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -1341,7 +1341,7 @@
         <v>119388484</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -1341,7 +1341,7 @@
         <v>119388484</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -1341,7 +1341,7 @@
         <v>119388484</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102223021</v>
+        <v>102223026</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590156.9894909392</v>
+        <v>590157</v>
       </c>
       <c r="R2" t="n">
-        <v>6927203.850608894</v>
+        <v>6927203</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2022-07-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102223026</v>
+        <v>119388655</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +810,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra sidan Lillån, öster om Hällsjön. Efter bron., Mpd</t>
+          <t>Väster om Korpipele, Lillström. Norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590156.9894909392</v>
+        <v>590222</v>
       </c>
       <c r="R3" t="n">
-        <v>6927203.850608894</v>
+        <v>6927173</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119388793</v>
+        <v>119388639</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,14 +911,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Korpipele, Lillström. Norra sidan ån. Nära vägen., Mpd</t>
+          <t>Väster om Korpipele, Lillström. Norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590192</v>
+        <v>590222</v>
       </c>
       <c r="R4" t="n">
-        <v>6927313</v>
+        <v>6927173</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1013,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119388763</v>
+        <v>102223021</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,38 +989,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Väster om Korpipele, Lillström. Norra sidan ån., Mpd</t>
+          <t>Norra sidan Lillån, öster om Hällsjön. Efter bron., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590186</v>
+        <v>590157</v>
       </c>
       <c r="R5" t="n">
-        <v>6927245</v>
+        <v>6927203</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1087,12 +1046,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2022-07-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119388639</v>
+        <v>119388531</v>
       </c>
       <c r="B6" t="n">
-        <v>91194</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,14 +1113,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Väster om Korpipele, Lillström. Norra sidan ån., Mpd</t>
+          <t>Korpipele, Lillström. Norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590222</v>
+        <v>590280</v>
       </c>
       <c r="R6" t="n">
-        <v>6927173</v>
+        <v>6927278</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1199,6 +1153,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Förekommer på flertalet äldre granar i området mellan ån och vägen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119388625</v>
+        <v>119388793</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1242,38 +1196,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Väster om Korpipele, Lillström. Norra sidan ån., Mpd</t>
+          <t>Korpipele, Lillström. Norra sidan ån. Nära vägen., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590222</v>
+        <v>590192</v>
       </c>
       <c r="R7" t="n">
-        <v>6927173</v>
+        <v>6927313</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1306,11 +1259,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Vid låga.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,15 +1286,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119388484</v>
+        <v>122670756</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57874</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,16 +1297,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1376,23 +1319,23 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>funnen död</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Korpipele, Lillström. Norra sidan ån., Mpd</t>
+          <t>Korpipele, vid mötesplats på vägen., Hällsjön, n:a Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590280</v>
+        <v>590339</v>
       </c>
       <c r="R8" t="n">
-        <v>6927278</v>
+        <v>6927305</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,17 +1359,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på gran, vet ej om de är färska eller ej.</t>
+          <t>Fjädrar vid mötesplats efter Lillströmsvägen vid Korpipele. Hål i vallen vid sidan av vägen med blodspår längst in.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,54 +1396,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119388706</v>
+        <v>119388484</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väster om korpipele, norra sidan ån., Mpd</t>
+          <t>Korpipele, Lillström. Norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590181</v>
+        <v>590280</v>
       </c>
       <c r="R9" t="n">
-        <v>6927213</v>
+        <v>6927278</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1537,7 +1479,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>I område anmält för avverkning. Svårt att få in exakta koordinater. Knärot utspridd i området.</t>
+          <t>Ringhack på gran, vet ej om de är färska eller ej.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,7 +1488,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1565,15 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119388546</v>
+        <v>116584290</v>
       </c>
       <c r="B10" t="n">
-        <v>96864</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,34 +1517,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224363</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Korpipele, Lillström. Norra sidan ån, nära vägen., Mpd</t>
+          <t>Lillström, Västatjärnarna. Vägren., Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590254</v>
+        <v>590443</v>
       </c>
       <c r="R10" t="n">
-        <v>6927321</v>
+        <v>6927311</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1635,17 +1580,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-05-04</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Stora mängder nära vägen.</t>
+          <t>Flertal grodor i parning. I diket vid vägkantens norra sida.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,15 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119388774</v>
+        <v>119388568</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1656,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -1717,10 +1671,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590160</v>
+        <v>590212</v>
       </c>
       <c r="R11" t="n">
-        <v>6927231</v>
+        <v>6927204</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1757,7 +1711,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Vid sten.</t>
+          <t>98 utblommade stänglar, desto fler bladrosetter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1785,15 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119388568</v>
+        <v>119388582</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1818,25 +1767,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Väster om Korpipele, Lillström. Norra sidan ån., Mpd</t>
+          <t>Väster om Korpipele, norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590212</v>
+        <v>590208</v>
       </c>
       <c r="R12" t="n">
-        <v>6927204</v>
+        <v>6927187</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1873,7 +1818,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>98 utblommade stänglar, desto fler bladrosetter.</t>
+          <t>Vid avbruten gran. Svårt att få in exakta koordinater i området.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1901,15 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119388744</v>
+        <v>119388625</v>
       </c>
       <c r="B13" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1945,10 +1885,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>590143</v>
+        <v>590222</v>
       </c>
       <c r="R13" t="n">
-        <v>6927229</v>
+        <v>6927173</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1981,6 +1921,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Vid låga.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2008,15 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119388582</v>
+        <v>119388706</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2048,14 +1988,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Väster om Korpipele, norra sidan ån., Mpd</t>
+          <t>Väster om korpipele, norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590208</v>
+        <v>590181</v>
       </c>
       <c r="R14" t="n">
-        <v>6927187</v>
+        <v>6927213</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2092,7 +2032,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Vid avbruten gran. Svårt att få in exakta koordinater i området.</t>
+          <t>I område anmält för avverkning. Svårt att få in exakta koordinater. Knärot utspridd i området.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,53 +2060,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119388531</v>
+        <v>119388744</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Korpipele, Lillström. Norra sidan ån., Mpd</t>
+          <t>Väster om Korpipele, Lillström. Norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590280</v>
+        <v>590143</v>
       </c>
       <c r="R15" t="n">
-        <v>6927278</v>
+        <v>6927229</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2199,11 +2135,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Förekommer på flertalet äldre granar i området mellan ån och vägen.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,35 +2162,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119388710</v>
+        <v>119388763</v>
       </c>
       <c r="B16" t="n">
-        <v>96864</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224363</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -2267,14 +2197,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väster om korpipele, norra sidan ån., Mpd</t>
+          <t>Väster om Korpipele, Lillström. Norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590181</v>
+        <v>590186</v>
       </c>
       <c r="R16" t="n">
-        <v>6927213</v>
+        <v>6927245</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2334,42 +2264,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119388655</v>
+        <v>119388774</v>
       </c>
       <c r="B17" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2377,10 +2303,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590222</v>
+        <v>590160</v>
       </c>
       <c r="R17" t="n">
-        <v>6927173</v>
+        <v>6927231</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2413,6 +2339,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Vid sten.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2440,57 +2371,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120107446</v>
+        <v>119388546</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>224363</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillström, korpipele., Mpd</t>
+          <t>Korpipele, Lillström. Norra sidan ån, nära vägen., Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>590246</v>
+        <v>590254</v>
       </c>
       <c r="R18" t="n">
-        <v>6927243</v>
+        <v>6927321</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2517,12 +2436,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Stora mängder nära vägen.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2550,61 +2474,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122670756</v>
+        <v>119388710</v>
       </c>
       <c r="B19" t="n">
-        <v>57369</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97985</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100001</v>
+        <v>224363</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Korpipele, vid mötesplats på vägen., Hällsjön, n:a Stöde, Mpd</t>
+          <t>Väster om korpipele, norra sidan ån., Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>590339</v>
+        <v>590181</v>
       </c>
       <c r="R19" t="n">
-        <v>6927305</v>
+        <v>6927213</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2628,17 +2539,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Fjädrar vid mötesplats efter Lillströmsvägen vid Korpipele. Hål i vallen vid sidan av vägen med blodspår längst in.</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2647,6 +2553,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 54345-2023 artfynd.xlsx
+++ b/artfynd/A 54345-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102223026</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388639</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102223021</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388531</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1283,6 +1313,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388793</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1393,6 +1428,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122670756</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388484</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116584290</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388568</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1843,6 +1898,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388582</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388625</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2057,6 +2122,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388706</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2159,6 +2229,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388744</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2261,6 +2336,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388763</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2368,6 +2448,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388774</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2471,6 +2556,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388546</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2569,8 +2659,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119388710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>